--- a/LEIP_sealane_correction.xlsx
+++ b/LEIP_sealane_correction.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B7"/>
+  <dimension ref="B2:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="2" max="2"/>
@@ -517,35 +517,28 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Each cell = sea-lane distance ÷ straight-line distance for that port pair. 1.00 = open water, no detour; higher = more land to round.</t>
+          <t>Each cell = navigable distance ÷ point-to-point for that port pair. 1.00 = open water; higher = more land to round.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Method: navigable path routed around Natural Earth Mediterranean coastline (visibility graph, shortest sea path). Covers all 33×33 pairs.</t>
+          <t>Method: shortest sea path routed around Natural Earth Med coastline. Short legs that round headlands (e.g. Bonifacio↔Porto Vecchio ×3.56) correctly keep a &gt;1 ratio.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Colour: green &lt;1.10 (near-direct) · amber &lt;1.35 · orange &lt;2.0 · red ≥2.0 (major detour, e.g. round the Italian boot).</t>
+          <t>Colour: green &lt;1.10 · amber &lt;1.35 · orange &lt;2.0 · red ≥2.0 (major detour).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>This REPLACES the blanket 1.52 factor. It approximates real routing but does not know traffic lanes/depth — flag any leg that looks wrong and it can be hand-set.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Ratio_Matrix tab: full 33×33. Notable_Legs tab: the pairs with the largest corrections, for quick review.</t>
+          <t>Approximates routing; does not know traffic lanes/depth — flag any leg to hand-set. sea_nm is on the pack distance-matrix basis.</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4388,7 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1179.8</v>
+        <v>1180.1</v>
       </c>
       <c r="D2" s="12" t="n">
         <v>7.493</v>
@@ -4418,7 +4411,7 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>1186.2</v>
+        <v>1199.6</v>
       </c>
       <c r="D3" s="12" t="n">
         <v>6.762</v>
@@ -4441,7 +4434,7 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>1202</v>
+        <v>1202.1</v>
       </c>
       <c r="D4" s="12" t="n">
         <v>5.155</v>
@@ -4487,7 +4480,7 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1207.2</v>
+        <v>1207.5</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>5.029</v>
@@ -4510,7 +4503,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1146</v>
+        <v>1139.2</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>4.923</v>
@@ -4556,7 +4549,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1215</v>
+        <v>1224</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>4.815</v>
@@ -4579,7 +4572,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1215.5</v>
+        <v>1224</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>4.422</v>
@@ -4625,7 +4618,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1055.4</v>
+        <v>1059.5</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>3.977</v>
@@ -4648,7 +4641,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1056.4</v>
+        <v>1056.5</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>3.776</v>
@@ -4671,7 +4664,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1034.4</v>
+        <v>1034.5</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>3.621</v>
@@ -4694,7 +4687,7 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>51.4</v>
+        <v>47.8</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>3.565</v>
@@ -4717,7 +4710,7 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1025.9</v>
+        <v>1032.2</v>
       </c>
       <c r="D16" s="12" t="n">
         <v>3.465</v>
@@ -4740,7 +4733,7 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1025</v>
+        <v>1042.8</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>3.446</v>
@@ -4763,7 +4756,7 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>52.9</v>
+        <v>63</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>3.389</v>
@@ -4786,7 +4779,7 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>99.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>3.026</v>
@@ -4809,7 +4802,7 @@
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>866</v>
+        <v>863.2</v>
       </c>
       <c r="D20" s="12" t="n">
         <v>2.991</v>
@@ -4832,7 +4825,7 @@
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>868</v>
+        <v>870.2</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>2.937</v>
@@ -4855,7 +4848,7 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>44</v>
+        <v>41.5</v>
       </c>
       <c r="D22" s="12" t="n">
         <v>2.926</v>
@@ -4878,7 +4871,7 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>848.1</v>
+        <v>846</v>
       </c>
       <c r="D23" s="12" t="n">
         <v>2.773</v>
@@ -4901,7 +4894,7 @@
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>558.6</v>
+        <v>562.4</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>2.738</v>
@@ -4924,7 +4917,7 @@
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>578.6</v>
+        <v>584.1</v>
       </c>
       <c r="D25" s="12" t="n">
         <v>2.723</v>
@@ -4947,7 +4940,7 @@
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>576.6</v>
+        <v>580.9</v>
       </c>
       <c r="D26" s="12" t="n">
         <v>2.632</v>
@@ -4970,7 +4963,7 @@
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>1024.1</v>
+        <v>1022.1</v>
       </c>
       <c r="D27" s="12" t="n">
         <v>2.556</v>
@@ -4993,7 +4986,7 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1326.3</v>
+        <v>1327.5</v>
       </c>
       <c r="D28" s="12" t="n">
         <v>2.395</v>
@@ -5016,7 +5009,7 @@
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1335</v>
+        <v>1334.9</v>
       </c>
       <c r="D29" s="12" t="n">
         <v>2.366</v>
@@ -5039,7 +5032,7 @@
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>32.6</v>
+        <v>28.2</v>
       </c>
       <c r="D30" s="12" t="n">
         <v>2.295</v>
@@ -5062,7 +5055,7 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>165.4</v>
+        <v>171.6</v>
       </c>
       <c r="D31" s="12" t="n">
         <v>2.255</v>
